--- a/outputs/daily/hr_rankings_2026-08-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-14.xlsx
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -16957,7 +16957,7 @@
         <v>50</v>
       </c>
       <c r="U61" t="n">
-        <v>71.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -32775,27 +32775,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>642851</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Austin Wynns</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-14T22:10:00Z</t>
+          <t>2026-08-15T01:40:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -32805,26 +32805,14 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Sandy Alcantara</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>645261</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -32838,26 +32826,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>13.3</v>
+        <v>18.4</v>
       </c>
       <c r="Q119" t="n">
-        <v>34.8</v>
+        <v>41.2</v>
       </c>
       <c r="R119" t="n">
-        <v>39.3</v>
+        <v>30.9</v>
       </c>
       <c r="S119" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>35.6</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -32871,7 +32859,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -32896,7 +32884,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -32913,12 +32901,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -32928,12 +32916,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 18.5 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -32943,104 +32931,80 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.15</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>97.828</t>
+          <t>97.7986</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.1247</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.2544</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>36.03</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.056</t>
-        </is>
-      </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>89.02</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>0.3877</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>0.1358</t>
-        </is>
-      </c>
-      <c r="BF119" t="inlineStr">
-        <is>
-          <t>23.96</t>
-        </is>
-      </c>
+          <t>0.1039</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -33051,12 +33015,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -33081,7 +33045,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -33114,11 +33078,11 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>29.7</v>
+        <v>13.3</v>
       </c>
       <c r="Q120" t="n">
         <v>34.8</v>
@@ -33127,13 +33091,13 @@
         <v>39.3</v>
       </c>
       <c r="S120" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T120" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -33147,7 +33111,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -33172,7 +33136,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -33194,7 +33158,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33204,12 +33168,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 18.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 18.5 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -33219,67 +33183,67 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>99.7529</t>
+          <t>97.828</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.197</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.2932</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.0885</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
@@ -33327,27 +33291,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>642851</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin Wynns</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-15T01:40:00Z</t>
+          <t>2026-08-14T22:10:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -33357,14 +33321,26 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Sandy Alcantara</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>645261</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L121" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -33382,22 +33358,22 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>18.4</v>
+        <v>29.7</v>
       </c>
       <c r="Q121" t="n">
-        <v>41.2</v>
+        <v>34.8</v>
       </c>
       <c r="R121" t="n">
-        <v>30.9</v>
+        <v>39.3</v>
       </c>
       <c r="S121" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T121" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U121" t="n">
-        <v>28.2</v>
+        <v>0.8</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33411,7 +33387,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -33436,7 +33412,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr"/>
@@ -33453,12 +33429,12 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -33468,12 +33444,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/13, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 18.5 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -33483,80 +33459,104 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>86.15</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>97.7986</t>
+          <t>99.7529</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1247</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.2544</t>
+          <t>0.2932</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1039</t>
-        </is>
-      </c>
-      <c r="BA121" t="inlineStr"/>
-      <c r="BB121" t="inlineStr"/>
-      <c r="BC121" t="inlineStr"/>
-      <c r="BD121" t="inlineStr"/>
-      <c r="BE121" t="inlineStr"/>
-      <c r="BF121" t="inlineStr"/>
+          <t>0.0885</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>89.02</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>0.3877</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr">
+        <is>
+          <t>0.1358</t>
+        </is>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>23.96</t>
+        </is>
+      </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-14.xlsx
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -43940,7 +43940,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -47016,7 +47016,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -50368,7 +50368,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -55376,7 +55376,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -58152,7 +58152,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -58712,7 +58712,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -59780,7 +59780,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -60620,7 +60620,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -62626,7 +62626,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-14.xlsx
@@ -4186,34 +4186,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5870,34 +5866,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8674,34 +8666,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10358,34 +10346,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12042,34 +12026,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -17086,34 +17066,30 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -20450,34 +20426,30 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -23814,34 +23786,30 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -24656,28 +24624,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -29688,34 +29660,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -31372,34 +31340,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
